--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92576940874</v>
+        <v>46157.93187910339</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93187910339</v>
+        <v>46157.93408468238</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93408468238</v>
+        <v>46157.93726170814</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93726170814</v>
+        <v>46158.28223710719</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28223710719</v>
+        <v>46158.29715456918</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29715456918</v>
+        <v>46158.29824101864</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29824101864</v>
+        <v>46158.33394827481</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33394827481</v>
+        <v>46158.36864525021</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36864525021</v>
+        <v>46158.37295501212</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
